--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -1140,11 +1140,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1257,11 +1253,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136868460</v>
       </c>
       <c r="B6" t="n">
-        <v>5498</v>
+        <v>5504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136868464</v>
       </c>
       <c r="B7" t="n">
-        <v>5498</v>
+        <v>5504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29167-2026 artfynd.xlsx
+++ b/artfynd/A 29167-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868463</v>
       </c>
       <c r="B2" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868462</v>
       </c>
       <c r="B3" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868461</v>
       </c>
       <c r="B4" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136868465</v>
       </c>
       <c r="B5" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>136868466</v>
       </c>
       <c r="B8" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
